--- a/salre/src/main/webapp/excel/contractTmp_last_output.xlsx
+++ b/salre/src/main/webapp/excel/contractTmp_last_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\git\salre\salre\src\main\webapp\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B600D02C-9C4D-4505-94CE-1751DFCAFF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF6C955-41D2-42E7-A6B3-358C1AAC0FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2670" windowWidth="29040" windowHeight="15720" xr2:uid="{71B69F57-4BB6-4C4A-ACD6-F195865104EA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{71B69F57-4BB6-4C4A-ACD6-F195865104EA}"/>
   </bookViews>
   <sheets>
     <sheet name="부동산임대차계약서" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="99">
   <si>
     <t>부동산임대차계약서</t>
   </si>
@@ -291,10 +291,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">    에게 인도하며, 임대차 기간은 인도일로부터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>제 3조 (</t>
     </r>
@@ -874,97 +870,90 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> 에게 인도하며, 임대차 기간은 인도일로부터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주민등록번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>경기도 시흥시 블바라 999-34</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>010-8987-9999</t>
+  </si>
+  <si>
+    <t>금오천만원정</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>철근콘크리트</t>
+  </si>
+  <si>
+    <t>다세대주택및제2종근린생활시설</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>010-4544-9343</t>
+  </si>
+  <si>
+    <t>박스프링</t>
+  </si>
+  <si>
+    <t>구로구 개봉동 제이원룸</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>22</t>
+    <t/>
+  </si>
+  <si>
+    <t>184.1분의12.483</t>
+  </si>
+  <si>
+    <t>031211-11111</t>
+  </si>
+  <si>
+    <t>이태한</t>
+  </si>
+  <si>
+    <t>월세</t>
+  </si>
+  <si>
+    <t>금일십오만원정</t>
+  </si>
+  <si>
+    <t>951111-222222</t>
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>경기도 시흥시 블바라 999-34</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>300,000</t>
-  </si>
-  <si>
-    <t>4,000,000</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>010-8987-9999</t>
-  </si>
-  <si>
-    <t>금오천만원정</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>철근콘크리트</t>
-  </si>
-  <si>
-    <t>다세대주택및제2종근린생활시설</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>010-4544-9343</t>
-  </si>
-  <si>
-    <t>박스프링</t>
-  </si>
-  <si>
-    <t>구로구 개봉동 제이원룸</t>
-  </si>
-  <si>
-    <t>500000</t>
-  </si>
-  <si>
-    <t>마르고 닳도록</t>
-  </si>
-  <si>
-    <t>봉준호 손흥민 레스고</t>
-  </si>
-  <si>
-    <t>임대인과 임차인은 계약에 충실한다.</t>
-  </si>
-  <si>
-    <t>동해물과 백두산이</t>
-  </si>
-  <si>
-    <t>184.1분의12.483</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>031211-11111</t>
-  </si>
-  <si>
-    <t>이태한</t>
-  </si>
-  <si>
-    <t>월세</t>
-  </si>
-  <si>
-    <t>금일십오만원정</t>
-  </si>
-  <si>
-    <t>951111-222222</t>
   </si>
   <si>
     <t>3층의 제303호 전유 전부</t>
@@ -984,7 +973,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1101,7 +1090,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1110,14 +1099,31 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1142,14 +1148,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="53">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1451,32 +1451,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1775,10 +1749,21 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1789,7 +1774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1811,10 +1796,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1832,107 +1817,110 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1940,147 +1928,171 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2102,53 +2114,35 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2487,23 +2481,23 @@
   <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="3.08203125"/>
+    <col min="1" max="1" customWidth="true" width="2.33203125"/>
     <col min="2" max="2" customWidth="true" width="5.9140625"/>
     <col min="3" max="3" customWidth="true" width="4.5"/>
     <col min="4" max="4" customWidth="true" width="4.08203125"/>
     <col min="5" max="5" customWidth="true" width="2.58203125"/>
     <col min="6" max="6" customWidth="true" width="2.9140625"/>
-    <col min="7" max="7" customWidth="true" width="5.25"/>
-    <col min="8" max="8" customWidth="true" width="3.4140625"/>
-    <col min="9" max="9" customWidth="true" width="2.6640625"/>
-    <col min="10" max="10" customWidth="true" width="5.6640625"/>
+    <col min="7" max="7" customWidth="true" width="5.6640625"/>
+    <col min="8" max="8" customWidth="true" width="4.75"/>
+    <col min="9" max="9" customWidth="true" width="2.1640625"/>
+    <col min="10" max="10" customWidth="true" width="6.08203125"/>
     <col min="11" max="11" customWidth="true" width="1.83203125"/>
     <col min="12" max="12" customWidth="true" width="3.75"/>
     <col min="13" max="13" customWidth="true" width="2.33203125"/>
-    <col min="14" max="14" customWidth="true" width="3.5"/>
-    <col min="15" max="15" customWidth="true" width="3.1640625"/>
-    <col min="16" max="16" customWidth="true" width="3.4140625"/>
-    <col min="17" max="17" customWidth="true" width="3.75"/>
+    <col min="14" max="14" customWidth="true" width="6.75"/>
+    <col min="15" max="15" customWidth="true" width="3.0"/>
+    <col min="16" max="16" customWidth="true" width="2.4140625"/>
+    <col min="17" max="17" customWidth="true" width="1.33203125"/>
     <col min="18" max="18" customWidth="true" width="2.33203125"/>
     <col min="19" max="20" customWidth="true" width="2.5"/>
     <col min="21" max="21" customWidth="true" width="2.25"/>
@@ -2516,43 +2510,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" x14ac:dyDescent="0.45">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="97" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="97"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="106" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="106"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -2576,497 +2570,497 @@
       <c r="Y2" s="5"/>
     </row>
     <row r="3" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="100"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="109"/>
     </row>
     <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="102"/>
-      <c r="T4" s="102"/>
-      <c r="U4" s="102"/>
-      <c r="V4" s="102"/>
-      <c r="W4" s="102"/>
-      <c r="X4" s="102"/>
-      <c r="Y4" s="103"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111"/>
+      <c r="Y4" s="112"/>
     </row>
     <row r="5" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="114" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="115"/>
-      <c r="W5" s="115"/>
-      <c r="X5" s="115"/>
-      <c r="Y5" s="117"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="113" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="114"/>
+      <c r="W5" s="114"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="116"/>
     </row>
     <row r="6" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="92" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="92"/>
-      <c r="E6" s="93" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="94" t="s">
+      <c r="D6" s="95"/>
+      <c r="E6" s="96" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="95"/>
-      <c r="P6" s="95"/>
-      <c r="Q6" s="108" t="s">
+      <c r="O6" s="98"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="R6" s="107"/>
-      <c r="S6" s="107"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="107"/>
-      <c r="V6" s="107"/>
-      <c r="W6" s="107"/>
-      <c r="X6" s="107"/>
+      <c r="R6" s="100"/>
+      <c r="S6" s="100"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="100"/>
       <c r="Y6" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92" t="s">
+      <c r="B7" s="94"/>
+      <c r="C7" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="93" t="s">
+      <c r="D7" s="95"/>
+      <c r="E7" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="100"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="94" t="s">
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="95"/>
+      <c r="O7" s="98"/>
       <c r="P7" s="33"/>
-      <c r="Q7" s="106" t="s">
-        <v>92</v>
-      </c>
-      <c r="R7" s="107"/>
-      <c r="S7" s="107"/>
-      <c r="T7" s="107"/>
-      <c r="U7" s="107"/>
-      <c r="V7" s="107"/>
-      <c r="W7" s="107"/>
-      <c r="X7" s="107"/>
+      <c r="Q7" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="100"/>
+      <c r="S7" s="100"/>
+      <c r="T7" s="100"/>
+      <c r="U7" s="100"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="100"/>
       <c r="Y7" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="112" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109" t="s">
-        <v>83</v>
-      </c>
-      <c r="R8" s="109"/>
-      <c r="S8" s="109"/>
-      <c r="T8" s="109"/>
-      <c r="U8" s="109"/>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="110"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="102"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102" t="s">
+        <v>82</v>
+      </c>
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="103"/>
     </row>
     <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="89"/>
-      <c r="J9" s="89"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="89"/>
-      <c r="M9" s="89"/>
-      <c r="N9" s="89"/>
-      <c r="O9" s="89"/>
-      <c r="P9" s="89"/>
-      <c r="Q9" s="89"/>
-      <c r="R9" s="89"/>
-      <c r="S9" s="89"/>
-      <c r="T9" s="89"/>
-      <c r="U9" s="89"/>
-      <c r="V9" s="89"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="90"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="92"/>
+      <c r="R9" s="92"/>
+      <c r="S9" s="92"/>
+      <c r="T9" s="92"/>
+      <c r="U9" s="92"/>
+      <c r="V9" s="92"/>
+      <c r="W9" s="92"/>
+      <c r="X9" s="92"/>
+      <c r="Y9" s="93"/>
     </row>
     <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="82"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="82"/>
-      <c r="T10" s="82"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="82"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="82"/>
-      <c r="Y10" s="83"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="83"/>
+      <c r="V10" s="83"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="84"/>
     </row>
     <row r="11" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="84" t="s">
+      <c r="B11" s="75"/>
+      <c r="C11" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="74"/>
-      <c r="T11" s="74"/>
-      <c r="U11" s="74"/>
-      <c r="V11" s="74"/>
-      <c r="W11" s="74"/>
-      <c r="X11" s="74"/>
-      <c r="Y11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="O11" s="86"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="87"/>
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="87" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="87"/>
-      <c r="N12" s="87"/>
-      <c r="O12" s="87"/>
-      <c r="P12" s="87"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30" t="s">
+      <c r="M12" s="90"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="90"/>
+      <c r="Q12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="Y12" s="86"/>
+      <c r="Y12" s="89"/>
     </row>
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="73" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="75" t="s">
+      <c r="K13" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="76"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="78"/>
+      <c r="U13" s="78"/>
+      <c r="V13" s="78"/>
+      <c r="W13" s="78"/>
+      <c r="X13" s="78"/>
+      <c r="Y13" s="79"/>
     </row>
     <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="79" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="75" t="s">
+      <c r="B14" s="81"/>
+      <c r="C14" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="75"/>
-      <c r="M14" s="75"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="76"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="78"/>
+      <c r="V14" s="78"/>
+      <c r="W14" s="78"/>
+      <c r="X14" s="78"/>
+      <c r="Y14" s="79"/>
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="54" t="s">
+      <c r="K15" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
-      <c r="W15" s="54"/>
-      <c r="X15" s="54"/>
-      <c r="Y15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="55"/>
+      <c r="P15" s="55"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="55"/>
+      <c r="T15" s="55"/>
+      <c r="U15" s="55"/>
+      <c r="V15" s="55"/>
+      <c r="W15" s="55"/>
+      <c r="X15" s="55"/>
+      <c r="Y15" s="56"/>
     </row>
     <row r="16" spans="1:25" ht="10" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="68" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F16" s="68"/>
       <c r="G16" s="68"/>
       <c r="H16" s="68"/>
       <c r="I16" s="68"/>
       <c r="J16" s="68"/>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="O16" s="64"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="64"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="64"/>
-      <c r="U16" s="64"/>
-      <c r="V16" s="64"/>
-      <c r="W16" s="64"/>
-      <c r="X16" s="64"/>
-      <c r="Y16" s="118"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="70"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="71"/>
     </row>
     <row r="17" spans="1:25" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="58"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="64"/>
       <c r="E17" s="69"/>
       <c r="F17" s="69"/>
       <c r="G17" s="69"/>
       <c r="H17" s="69"/>
       <c r="I17" s="69"/>
       <c r="J17" s="69"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="65"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="65"/>
-      <c r="Y17" s="119"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="72"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="73"/>
     </row>
     <row r="18" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
@@ -3084,23 +3078,23 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
-      <c r="O18" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
+      <c r="O18" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
       <c r="R18" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="S18" s="66" t="s">
+      <c r="S18" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="T18" s="66"/>
+      <c r="T18" s="67"/>
       <c r="U18" s="8" t="s">
         <v>28</v>
       </c>
       <c r="V18" s="67" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="W18" s="67"/>
       <c r="X18" s="9" t="s">
@@ -3109,28 +3103,28 @@
       <c r="Y18" s="8"/>
     </row>
     <row r="19" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="11" t="s">
-        <v>68</v>
+      <c r="A19" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J19" s="11" t="s">
-        <v>71</v>
+      <c r="J19" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="14" t="s">
         <v>72</v>
       </c>
       <c r="M19" s="10" t="s">
@@ -3150,459 +3144,459 @@
       <c r="Y19" s="10"/>
     </row>
     <row r="20" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="39"/>
+    </row>
+    <row r="21" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="39"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="39"/>
+      <c r="X21" s="39"/>
+      <c r="Y21" s="39"/>
+    </row>
+    <row r="22" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-    </row>
-    <row r="21" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-    </row>
-    <row r="22" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="41" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="39"/>
+    </row>
+    <row r="23" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="39"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="39"/>
+    </row>
+    <row r="24" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="41"/>
-      <c r="Y22" s="41"/>
-    </row>
-    <row r="23" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="41"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="41"/>
-      <c r="X23" s="41"/>
-      <c r="Y23" s="41"/>
-    </row>
-    <row r="24" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="41" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="39"/>
+    </row>
+    <row r="25" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39"/>
+      <c r="S25" s="39"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="39"/>
+    </row>
+    <row r="26" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="41"/>
-      <c r="Y24" s="41"/>
-    </row>
-    <row r="25" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="41"/>
-    </row>
-    <row r="26" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="41" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+    </row>
+    <row r="27" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="39"/>
+      <c r="V27" s="39"/>
+      <c r="W27" s="39"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="39"/>
+    </row>
+    <row r="28" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="41"/>
-    </row>
-    <row r="27" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
-      <c r="X27" s="41"/>
-      <c r="Y27" s="41"/>
-    </row>
-    <row r="28" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="41" t="s">
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+    </row>
+    <row r="29" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+    </row>
+    <row r="30" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="39"/>
+      <c r="V30" s="39"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="39"/>
+    </row>
+    <row r="31" spans="1:25" ht="11" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-    </row>
-    <row r="29" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-    </row>
-    <row r="30" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="41"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="41"/>
-      <c r="Y30" s="41"/>
-    </row>
-    <row r="31" spans="1:25" ht="11" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="41" t="s">
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="39"/>
+      <c r="X31" s="39"/>
+      <c r="Y31" s="39"/>
+    </row>
+    <row r="32" spans="1:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+    </row>
+    <row r="33" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
+    </row>
+    <row r="34" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="41"/>
-    </row>
-    <row r="32" spans="1:25" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="40"/>
-      <c r="S32" s="40"/>
-      <c r="T32" s="40"/>
-      <c r="U32" s="40"/>
-      <c r="V32" s="40"/>
-      <c r="W32" s="40"/>
-      <c r="X32" s="40"/>
-      <c r="Y32" s="40"/>
-    </row>
-    <row r="33" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="40"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="40"/>
-      <c r="U33" s="40"/>
-      <c r="V33" s="40"/>
-      <c r="W33" s="40"/>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="40"/>
-    </row>
-    <row r="34" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="41"/>
-      <c r="Y34" s="41"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="39"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="39"/>
     </row>
     <row r="35" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="10"/>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="14" t="s">
         <v>69</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="14" t="s">
         <v>71</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="11" t="s">
-        <v>93</v>
+      <c r="G35" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>41</v>
@@ -3655,186 +3649,180 @@
       <c r="Y36" s="5"/>
     </row>
     <row r="37" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
-      <c r="R37" s="37"/>
-      <c r="S37" s="37"/>
-      <c r="T37" s="37"/>
-      <c r="U37" s="37"/>
-      <c r="V37" s="37"/>
-      <c r="W37" s="37"/>
-      <c r="X37" s="37"/>
-      <c r="Y37" s="37"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="121" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="121"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
+      <c r="U37" s="121"/>
+      <c r="V37" s="121"/>
+      <c r="W37" s="121"/>
+      <c r="X37" s="121"/>
+      <c r="Y37" s="121"/>
     </row>
     <row r="38" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="37"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-      <c r="Q38" s="37"/>
-      <c r="R38" s="37"/>
-      <c r="S38" s="37"/>
-      <c r="T38" s="37"/>
-      <c r="U38" s="37"/>
-      <c r="V38" s="37"/>
-      <c r="W38" s="37"/>
-      <c r="X38" s="37"/>
-      <c r="Y38" s="37"/>
+      <c r="C38" s="121"/>
+      <c r="D38" s="121"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="121"/>
+      <c r="H38" s="121"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="121"/>
+      <c r="K38" s="121"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="121"/>
+      <c r="R38" s="121"/>
+      <c r="S38" s="121"/>
+      <c r="T38" s="121"/>
+      <c r="U38" s="121"/>
+      <c r="V38" s="121"/>
+      <c r="W38" s="121"/>
+      <c r="X38" s="121"/>
+      <c r="Y38" s="121"/>
     </row>
     <row r="39" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="37"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
-      <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="37"/>
+      <c r="C39" s="121"/>
+      <c r="D39" s="121"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="121"/>
+      <c r="H39" s="121"/>
+      <c r="I39" s="121"/>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
+      <c r="L39" s="121"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="121"/>
+      <c r="R39" s="121"/>
+      <c r="S39" s="121"/>
+      <c r="T39" s="121"/>
+      <c r="U39" s="121"/>
+      <c r="V39" s="121"/>
+      <c r="W39" s="121"/>
+      <c r="X39" s="121"/>
+      <c r="Y39" s="121"/>
     </row>
     <row r="40" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="37"/>
-      <c r="Q40" s="37"/>
-      <c r="R40" s="37"/>
-      <c r="S40" s="37"/>
-      <c r="T40" s="37"/>
-      <c r="U40" s="37"/>
-      <c r="V40" s="37"/>
-      <c r="W40" s="37"/>
-      <c r="X40" s="37"/>
-      <c r="Y40" s="37"/>
+      <c r="C40" s="121"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="121"/>
+      <c r="K40" s="121"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="121"/>
+      <c r="R40" s="121"/>
+      <c r="S40" s="121"/>
+      <c r="T40" s="121"/>
+      <c r="U40" s="121"/>
+      <c r="V40" s="121"/>
+      <c r="W40" s="121"/>
+      <c r="X40" s="121"/>
+      <c r="Y40" s="121"/>
     </row>
     <row r="41" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="37"/>
-      <c r="V41" s="37"/>
-      <c r="W41" s="37"/>
-      <c r="X41" s="37"/>
-      <c r="Y41" s="37"/>
+      <c r="C41" s="121"/>
+      <c r="D41" s="121"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="121"/>
+      <c r="G41" s="121"/>
+      <c r="H41" s="121"/>
+      <c r="I41" s="121"/>
+      <c r="J41" s="121"/>
+      <c r="K41" s="121"/>
+      <c r="L41" s="121"/>
+      <c r="M41" s="121"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="121"/>
+      <c r="P41" s="121"/>
+      <c r="Q41" s="121"/>
+      <c r="R41" s="121"/>
+      <c r="S41" s="121"/>
+      <c r="T41" s="121"/>
+      <c r="U41" s="121"/>
+      <c r="V41" s="121"/>
+      <c r="W41" s="121"/>
+      <c r="X41" s="121"/>
+      <c r="Y41" s="121"/>
     </row>
     <row r="42" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37"/>
-      <c r="M42" s="37"/>
-      <c r="N42" s="37"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="37"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-      <c r="U42" s="37"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="37"/>
-      <c r="Y42" s="37"/>
+      <c r="C42" s="121"/>
+      <c r="D42" s="121"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="121"/>
+      <c r="H42" s="121"/>
+      <c r="I42" s="121"/>
+      <c r="J42" s="121"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="121"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="121"/>
+      <c r="P42" s="121"/>
+      <c r="Q42" s="121"/>
+      <c r="R42" s="121"/>
+      <c r="S42" s="121"/>
+      <c r="T42" s="121"/>
+      <c r="U42" s="121"/>
+      <c r="V42" s="121"/>
+      <c r="W42" s="121"/>
+      <c r="X42" s="121"/>
+      <c r="Y42" s="121"/>
     </row>
     <row r="43" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
@@ -3843,29 +3831,29 @@
       <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="37"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-      <c r="U43" s="37"/>
-      <c r="V43" s="37"/>
-      <c r="W43" s="37"/>
-      <c r="X43" s="37"/>
-      <c r="Y43" s="37"/>
+      <c r="C43" s="122"/>
+      <c r="D43" s="122"/>
+      <c r="E43" s="122"/>
+      <c r="F43" s="122"/>
+      <c r="G43" s="122"/>
+      <c r="H43" s="122"/>
+      <c r="I43" s="122"/>
+      <c r="J43" s="122"/>
+      <c r="K43" s="122"/>
+      <c r="L43" s="122"/>
+      <c r="M43" s="122"/>
+      <c r="N43" s="122"/>
+      <c r="O43" s="122"/>
+      <c r="P43" s="122"/>
+      <c r="Q43" s="122"/>
+      <c r="R43" s="122"/>
+      <c r="S43" s="122"/>
+      <c r="T43" s="122"/>
+      <c r="U43" s="122"/>
+      <c r="V43" s="122"/>
+      <c r="W43" s="122"/>
+      <c r="X43" s="122"/>
+      <c r="Y43" s="122"/>
     </row>
     <row r="44" spans="1:25" ht="3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="3"/>
@@ -3895,59 +3883,59 @@
       <c r="Y44" s="12"/>
     </row>
     <row r="45" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
-      <c r="X45" s="41"/>
-      <c r="Y45" s="41"/>
+      <c r="A45" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="39"/>
+      <c r="S45" s="39"/>
+      <c r="T45" s="39"/>
+      <c r="U45" s="39"/>
+      <c r="V45" s="39"/>
+      <c r="W45" s="39"/>
+      <c r="X45" s="39"/>
+      <c r="Y45" s="39"/>
     </row>
     <row r="46" spans="1:25" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="15" t="s">
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="I46" s="15"/>
+      <c r="I46" s="47"/>
       <c r="J46" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="15" t="s">
         <v>71</v>
       </c>
       <c r="L46" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M46" s="11" t="s">
-        <v>93</v>
+      <c r="M46" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="N46" s="10" t="s">
         <v>44</v>
@@ -3965,37 +3953,37 @@
       <c r="Y46" s="10"/>
     </row>
     <row r="47" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="42" t="s">
+      <c r="A47" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="43" t="s">
+      <c r="B47" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="44"/>
-      <c r="D47" s="45" t="s">
+      <c r="C47" s="42"/>
+      <c r="D47" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="46"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="46"/>
-      <c r="S47" s="46"/>
-      <c r="T47" s="46"/>
-      <c r="U47" s="46"/>
-      <c r="V47" s="46"/>
-      <c r="W47" s="46"/>
-      <c r="X47" s="47"/>
-      <c r="Y47" s="36" t="s">
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="44"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="44"/>
+      <c r="X47" s="45"/>
+      <c r="Y47" s="48" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4006,7 +3994,7 @@
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="21" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -4017,7 +4005,7 @@
       </c>
       <c r="J48" s="28"/>
       <c r="K48" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L48" s="30"/>
       <c r="M48" s="30"/>
@@ -4032,7 +4020,7 @@
       </c>
       <c r="U48" s="33"/>
       <c r="V48" s="29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="W48" s="30"/>
       <c r="X48" s="31"/>
@@ -4053,10 +4041,10 @@
       <c r="F49" s="22"/>
       <c r="G49" s="22"/>
       <c r="H49" s="23"/>
-      <c r="I49" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="J49" s="39"/>
+      <c r="I49" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="J49" s="37"/>
       <c r="K49" s="29" t="s">
         <v>6</v>
       </c>
@@ -4088,7 +4076,7 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -4121,7 +4109,7 @@
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -4132,7 +4120,7 @@
       </c>
       <c r="J51" s="28"/>
       <c r="K51" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
@@ -4147,7 +4135,7 @@
       </c>
       <c r="U51" s="33"/>
       <c r="V51" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W51" s="30"/>
       <c r="X51" s="31"/>
@@ -4169,7 +4157,7 @@
       <c r="G52" s="22"/>
       <c r="H52" s="23"/>
       <c r="I52" s="34" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="J52" s="35"/>
       <c r="K52" s="29" t="s">
@@ -4209,7 +4197,7 @@
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="107">
+  <mergeCells count="101">
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -4219,7 +4207,8 @@
     <mergeCell ref="C5:Y5"/>
     <mergeCell ref="Q7:X7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:M8"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="A9:Y9"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -4228,9 +4217,8 @@
     <mergeCell ref="Q6:X6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:M7"/>
     <mergeCell ref="N7:P7"/>
+    <mergeCell ref="C8:Y8"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="K13:Y13"/>
@@ -4269,21 +4257,13 @@
     <mergeCell ref="A33:Y33"/>
     <mergeCell ref="A34:Y34"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:Y37"/>
     <mergeCell ref="A25:Y25"/>
     <mergeCell ref="A26:Y26"/>
     <mergeCell ref="A27:Y27"/>
     <mergeCell ref="A28:Y28"/>
     <mergeCell ref="A29:Y29"/>
     <mergeCell ref="A30:Y30"/>
-    <mergeCell ref="C38:Y38"/>
-    <mergeCell ref="C39:Y39"/>
-    <mergeCell ref="C40:Y40"/>
-    <mergeCell ref="C41:Y41"/>
-    <mergeCell ref="C42:Y42"/>
-    <mergeCell ref="C43:Y43"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="V48:X48"/>
+    <mergeCell ref="C37:Y43"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="E49:H49"/>
     <mergeCell ref="I49:J49"/>
@@ -4296,6 +4276,11 @@
     <mergeCell ref="D47:X47"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="H46:I46"/>
+    <mergeCell ref="Y47:Y49"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:S48"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="D50:X50"/>
@@ -4312,11 +4297,8 @@
     <mergeCell ref="K52:S52"/>
     <mergeCell ref="T52:U52"/>
     <mergeCell ref="V52:X52"/>
-    <mergeCell ref="Y47:Y49"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="V48:X48"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
